--- a/artfynd/A 57511-2023 artfynd.xlsx
+++ b/artfynd/A 57511-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57511-2023 artfynd.xlsx
+++ b/artfynd/A 57511-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -809,6 +809,121 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>115007514</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Myren, Tjärnö, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>279755</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6531842</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tjärnö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosök på stående död ved</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Maria Kuylenstierna</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Maria Kuylenstierna</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
